--- a/src/static/uploads/plantilla_votantes.xlsx
+++ b/src/static/uploads/plantilla_votantes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISTAE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92592630-4FC1-4307-915A-5E8F07D2D8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69C830A-BDA9-4E5B-A201-C3C6A760E849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>CÉDULA</t>
   </si>
@@ -31,12 +31,6 @@
     <t>APELLIDOS</t>
   </si>
   <si>
-    <t>Juan Perez</t>
-  </si>
-  <si>
-    <t>Maria</t>
-  </si>
-  <si>
     <t>0803913599</t>
   </si>
   <si>
@@ -52,18 +46,45 @@
     <t>0850195546</t>
   </si>
   <si>
+    <t>0803624741</t>
+  </si>
+  <si>
     <t>0803623529</t>
   </si>
   <si>
     <t>0804174811</t>
   </si>
   <si>
-    <t>0803624741</t>
-  </si>
-  <si>
     <t>1753610920</t>
   </si>
   <si>
+    <t>CABEZAS ALVAREZ</t>
+  </si>
+  <si>
+    <t>CANCHE MONTAÑO</t>
+  </si>
+  <si>
+    <t>COLOBON ARBOLEDA</t>
+  </si>
+  <si>
+    <t>NAPA AVEIGA</t>
+  </si>
+  <si>
+    <t>QUINTERO PRECIADO</t>
+  </si>
+  <si>
+    <t>REQUENE CHICHANDE</t>
+  </si>
+  <si>
+    <t>REQUENE VALENCIA</t>
+  </si>
+  <si>
+    <t>REQUENE VELASCO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ MARQUINEZ</t>
+  </si>
+  <si>
     <t>DARWIN DAVID</t>
   </si>
   <si>
@@ -79,43 +100,16 @@
     <t>NATALIA CRISTINA</t>
   </si>
   <si>
+    <t>DANIELA MERCEDES</t>
+  </si>
+  <si>
     <t>DANIELA MARIUXI</t>
   </si>
   <si>
     <t>ROMINA LILIANA</t>
   </si>
   <si>
-    <t>DANIELA MERCEDES</t>
-  </si>
-  <si>
     <t>JENIFER ALEXANDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABEZAS ALVAREZ </t>
-  </si>
-  <si>
-    <t>CANCHE MONTAÑO</t>
-  </si>
-  <si>
-    <t>COLOBON ARBOLEDA</t>
-  </si>
-  <si>
-    <t>NAPA AVEIGA</t>
-  </si>
-  <si>
-    <t>QUINTERO PRECIADO</t>
-  </si>
-  <si>
-    <t>REQUENE VALENCIA</t>
-  </si>
-  <si>
-    <t>REQUENE VELASCO</t>
-  </si>
-  <si>
-    <t>REQUENE CHICHANDE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ MARQUINEZ</t>
   </si>
 </sst>
 </file>
@@ -151,8 +145,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,15 +451,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="21.21875" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -474,103 +469,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
